--- a/results/supplementary/Supplementary_Table_S3_enrichment.xlsx
+++ b/results/supplementary/Supplementary_Table_S3_enrichment.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Locus-level enrichment'!$A$1:$U$256</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Relative contrasts'!$A$1:$H$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Relative contrasts'!$A$1:$I$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MAGMA gene-set'!$A$1:$L$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MAGMA monoamine LOO'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Locus x set hits'!$A$1:$D$2649</definedName>
@@ -487,7 +487,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Observed loci containing &gt;= 1 gene of each set vs matched null loci (10,000 permutations; exact Poisson-binomial p-values) for each analysis: primary (r2 &gt;= 0.6), r2 &gt;= 0.5, r2 &gt;= 0.8, MHC/17q21.31 excluded, and nearest gene. Null loci are matched on MAF, LD partners, gene count and distance to the nearest gene. fold_analytic = observed / expected (exact) loci; q = Benjamini-Hochberg within set family.</t>
+          <t>Observed loci containing &gt;= 1 gene of each set vs matched null loci (10,000 permutations; exact Poisson-binomial p-values) for each analysis: primary (r2 &gt;= 0.6), r2 &gt;= 0.5, r2 &gt;= 0.8, MHC/17q21.31 excluded, and nearest gene. Null loci are matched on MAF, LD partners, gene count and distance to the nearest gene. fold_analytic = observed / expected (exact) loci; q = Benjamini-Hochberg within set family. frac_of_mendelian_obs / _exp and p_relative: among loci containing a Mendelian gene, the fraction that also contain a gene of the set, observed vs matched null (same draws).</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Pre-specified contrasts: fraction of loci hitting set A among loci hitting set B, observed vs matched null.</t>
+          <t>Pre-specified contrasts: among loci containing a gene of the reference set (denominator), the fraction that also contain a gene of the phenotype set (numerator; obs_both = loci containing a gene of both), observed vs the same fraction in the matched null loci (same 10,000 draws).</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
         <v>0.089620793278487</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1221211212212112</v>
+        <v>0.3051694830516948</v>
       </c>
     </row>
     <row r="5">
@@ -951,13 +951,13 @@
         <v>0.0803919608039196</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.6260162601626016</v>
+        <v>0.5934959349593496</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.5634932138683709</v>
+        <v>0.5552855027989969</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0915908409159084</v>
+        <v>0.2042795720427957</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>64.80716613282675</v>
@@ -978,7 +978,7 @@
         <v>0.089620793278487</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1221211212212112</v>
+        <v>0.3491650834916508</v>
       </c>
     </row>
     <row r="6">
@@ -1024,13 +1024,13 @@
         <v>0.1077892210778922</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.9105691056910568</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.864460997930901</v>
+        <v>0.8562532868615271</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0835916408359164</v>
+        <v>0.2618738126187381</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>99.37840731453116</v>
@@ -1051,7 +1051,7 @@
         <v>0.089620793278487</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1221211212212112</v>
+        <v>0.3491650834916508</v>
       </c>
     </row>
     <row r="7">
@@ -4236,10 +4236,10 @@
         <v>0.0001999800019998</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.1788617886178861</v>
+        <v>0.1138211382113821</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.0392833360185812</v>
+        <v>0.0258211574111383</v>
       </c>
       <c r="N50" s="2" t="n">
         <v>9.999000099990002e-05</v>
@@ -4309,13 +4309,13 @@
         <v>0.0013998600139986</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.8536585365853658</v>
+        <v>0.5040650406504065</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.7223196790125069</v>
+        <v>0.4123408505786314</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0475952404759524</v>
+        <v>0.0188981101889811</v>
       </c>
       <c r="O51" s="2" t="n">
         <v>82.84241408387359</v>
@@ -4336,7 +4336,7 @@
         <v>0.0028810506542635</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>0.0951904809519048</v>
+        <v>0.0377962203779622</v>
       </c>
     </row>
     <row r="52">
@@ -4382,13 +4382,13 @@
         <v>0.7715228477152285</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.3577235772357723</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.3671524759380265</v>
+        <v>0.2398235323553074</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.5674432556744325</v>
+        <v>0.1111888811118888</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>42.01396871737703</v>
@@ -4409,7 +4409,7 @@
         <v>0.3837324973981432</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>0.5674432556744325</v>
+        <v>0.1111888811118888</v>
       </c>
     </row>
     <row r="53">
@@ -4620,7 +4620,7 @@
         <v>0.1018819182155731</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>0.18664800186648</v>
+        <v>0.406959304069593</v>
       </c>
     </row>
     <row r="56">
@@ -4666,13 +4666,13 @@
         <v>0.0605939406059394</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.6356589147286822</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.5754057167452798</v>
+        <v>0.5677071940790375</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0921907809219078</v>
+        <v>0.2034796520347965</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>69.07987515063762</v>
@@ -4693,7 +4693,7 @@
         <v>0.1018819182155731</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>0.18664800186648</v>
+        <v>0.406959304069593</v>
       </c>
     </row>
     <row r="57">
@@ -4739,13 +4739,13 @@
         <v>0.1173882611738826</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.9069767441860463</v>
+        <v>0.875968992248062</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.8726201247807011</v>
+        <v>0.8649216021144588</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.13998600139986</v>
+        <v>0.3785621437856214</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>104.8117287290386</v>
@@ -4766,7 +4766,7 @@
         <v>0.1018819182155731</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>0.18664800186648</v>
+        <v>0.5047495250474953</v>
       </c>
     </row>
     <row r="58">
@@ -7951,13 +7951,13 @@
         <v>0.0001999800019998</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0.1705426356589147</v>
+        <v>0.1085271317829457</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>0.0398454047436592</v>
+        <v>0.027658447941401</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>9.999000099990002e-05</v>
+        <v>0.0001999800019998</v>
       </c>
       <c r="O101" s="2" t="n">
         <v>4.772023343641344</v>
@@ -7978,7 +7978,7 @@
         <v>2.573785487531196e-09</v>
       </c>
       <c r="U101" s="2" t="n">
-        <v>9.999000099990002e-05</v>
+        <v>0.0001999800019998</v>
       </c>
     </row>
     <row r="102">
@@ -8024,13 +8024,13 @@
         <v>0.0103989601039896</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>0.7428820154624318</v>
+        <v>0.4395817850450215</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1028897110288971</v>
+        <v>0.0533946605339466</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>88.92938133745136</v>
@@ -8051,7 +8051,7 @@
         <v>0.0112075610958169</v>
       </c>
       <c r="U102" s="2" t="n">
-        <v>0.2057794220577942</v>
+        <v>0.1067893210678932</v>
       </c>
     </row>
     <row r="103">
@@ -8097,13 +8097,13 @@
         <v>0.2765723427657234</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0.4031007751937984</v>
+        <v>0.3100775193798449</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>0.3828558951920594</v>
+        <v>0.2658121694311969</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.3331666833316668</v>
+        <v>0.122987701229877</v>
       </c>
       <c r="O103" s="2" t="n">
         <v>45.78345871667848</v>
@@ -8124,7 +8124,7 @@
         <v>0.1456454990761581</v>
       </c>
       <c r="U103" s="2" t="n">
-        <v>0.3331666833316668</v>
+        <v>0.122987701229877</v>
       </c>
     </row>
     <row r="104">
@@ -8335,7 +8335,7 @@
         <v>0.2276569507756033</v>
       </c>
       <c r="U106" s="2" t="n">
-        <v>0.3474319234743192</v>
+        <v>0.5805419458054195</v>
       </c>
     </row>
     <row r="107">
@@ -8381,13 +8381,13 @@
         <v>0.2045795420457954</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0.5871559633027523</v>
+        <v>0.5596330275229358</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>0.5414193734870819</v>
+        <v>0.5325189692471652</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1821817818218178</v>
+        <v>0.2902709729027097</v>
       </c>
       <c r="O107" s="2" t="n">
         <v>55.38747882364076</v>
@@ -8408,7 +8408,7 @@
         <v>0.2276569507756033</v>
       </c>
       <c r="U107" s="2" t="n">
-        <v>0.3474319234743192</v>
+        <v>0.5805419458054195</v>
       </c>
     </row>
     <row r="108">
@@ -8454,13 +8454,13 @@
         <v>0.2727727227277272</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0.8807339449541285</v>
+        <v>0.8532110091743119</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>0.856801184999199</v>
+        <v>0.8479007807592821</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.2605739426057394</v>
+        <v>0.4515548445155484</v>
       </c>
       <c r="O108" s="2" t="n">
         <v>87.54373463581101</v>
@@ -8481,7 +8481,7 @@
         <v>0.2276569507756033</v>
       </c>
       <c r="U108" s="2" t="n">
-        <v>0.3474319234743192</v>
+        <v>0.6020731260207313</v>
       </c>
     </row>
     <row r="109">
@@ -11666,13 +11666,13 @@
         <v>0.0001999800019998</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0.146788990825688</v>
+        <v>0.0825688073394495</v>
       </c>
       <c r="M152" s="2" t="n">
-        <v>0.0397166256092055</v>
+        <v>0.0251761416812964</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>9.999000099990002e-05</v>
+        <v>0.0015998400159984</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>4.019905884874278</v>
@@ -11693,7 +11693,7 @@
         <v>2.640708485466124e-06</v>
       </c>
       <c r="U152" s="2" t="n">
-        <v>9.999000099990002e-05</v>
+        <v>0.0015998400159984</v>
       </c>
     </row>
     <row r="153">
@@ -11739,13 +11739,13 @@
         <v>0.0009999000099990001</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>0.8715596330275229</v>
+        <v>0.4678899082568807</v>
       </c>
       <c r="M153" s="2" t="n">
-        <v>0.7003786228450787</v>
+        <v>0.3620766166199181</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.0274972502749725</v>
+        <v>0.0115988401159884</v>
       </c>
       <c r="O153" s="2" t="n">
         <v>71.16634066235302</v>
@@ -11766,7 +11766,7 @@
         <v>0.0009972950035416</v>
       </c>
       <c r="U153" s="2" t="n">
-        <v>0.054994500549945</v>
+        <v>0.0231976802319768</v>
       </c>
     </row>
     <row r="154">
@@ -11812,13 +11812,13 @@
         <v>0.6401359864013598</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0.3119266055045872</v>
+        <v>0.2293577981651376</v>
       </c>
       <c r="M154" s="2" t="n">
-        <v>0.3086768674383502</v>
+        <v>0.1797106529578697</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.4627537246275372</v>
+        <v>0.0887911208879112</v>
       </c>
       <c r="O154" s="2" t="n">
         <v>31.38183367925763</v>
@@ -11839,7 +11839,7 @@
         <v>0.3255292327197683</v>
       </c>
       <c r="U154" s="2" t="n">
-        <v>0.4627537246275372</v>
+        <v>0.0887911208879112</v>
       </c>
     </row>
     <row r="155">
@@ -12050,7 +12050,7 @@
         <v>0.095900702337647</v>
       </c>
       <c r="U157" s="2" t="n">
-        <v>0.2110455621104556</v>
+        <v>0.4487551244875512</v>
       </c>
     </row>
     <row r="158">
@@ -12096,13 +12096,13 @@
         <v>0.11998800119988</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0.6198347107438017</v>
+        <v>0.5867768595041323</v>
       </c>
       <c r="M158" s="2" t="n">
-        <v>0.5731369292114054</v>
+        <v>0.5646371803180116</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.1582841715828417</v>
+        <v>0.3102689731026897</v>
       </c>
       <c r="O158" s="2" t="n">
         <v>64.04786274318603</v>
@@ -12123,7 +12123,7 @@
         <v>0.095900702337647</v>
       </c>
       <c r="U158" s="2" t="n">
-        <v>0.2110455621104556</v>
+        <v>0.4487551244875512</v>
       </c>
     </row>
     <row r="159">
@@ -12169,13 +12169,13 @@
         <v>0.0991900809919008</v>
       </c>
       <c r="L159" s="2" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8760330578512396</v>
       </c>
       <c r="M159" s="2" t="n">
-        <v>0.8696978055276062</v>
+        <v>0.8611980566342124</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.1240875912408759</v>
+        <v>0.3365663433656634</v>
       </c>
       <c r="O159" s="2" t="n">
         <v>97.27514905118996</v>
@@ -12196,7 +12196,7 @@
         <v>0.095900702337647</v>
       </c>
       <c r="U159" s="2" t="n">
-        <v>0.2110455621104556</v>
+        <v>0.4487551244875512</v>
       </c>
     </row>
     <row r="160">
@@ -15381,10 +15381,10 @@
         <v>0.0001999800019998</v>
       </c>
       <c r="L203" s="2" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1157024793388429</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>0.0404031829774836</v>
+        <v>0.0263158964317289</v>
       </c>
       <c r="N203" s="2" t="n">
         <v>9.999000099990002e-05</v>
@@ -15454,13 +15454,13 @@
         <v>0.0023997600239976</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>0.859504132231405</v>
+        <v>0.5041322314049587</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>0.7267406580302948</v>
+        <v>0.4108332450833574</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>0.0446955304469553</v>
+        <v>0.01999800019998</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>80.98245226573619</v>
@@ -15481,7 +15481,7 @@
         <v>0.0018248517089008</v>
       </c>
       <c r="U204" s="2" t="n">
-        <v>0.08939106089391061</v>
+        <v>0.03999600039996</v>
       </c>
     </row>
     <row r="205">
@@ -15527,13 +15527,13 @@
         <v>0.4955504449555044</v>
       </c>
       <c r="L205" s="2" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.2892561983471074</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>0.3595959217913863</v>
+        <v>0.2302963319806241</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.4548545145485451</v>
+        <v>0.0573942605739426</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>40.00937221307254</v>
@@ -15554,7 +15554,7 @@
         <v>0.2471726152041231</v>
       </c>
       <c r="U205" s="2" t="n">
-        <v>0.4548545145485451</v>
+        <v>0.0573942605739426</v>
       </c>
     </row>
     <row r="206">
@@ -15811,13 +15811,13 @@
         <v>0.6505349465053495</v>
       </c>
       <c r="L209" s="2" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>0.4972776935559123</v>
+        <v>0.4856858561222481</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0450954904509549</v>
+        <v>0.1253874612538746</v>
       </c>
       <c r="O209" s="2" t="n">
         <v>52.57587925606506</v>
@@ -15838,7 +15838,7 @@
         <v>0.8921744779830265</v>
       </c>
       <c r="U209" s="2" t="n">
-        <v>0.0901909809019098</v>
+        <v>0.2394427223944272</v>
       </c>
     </row>
     <row r="210">
@@ -15884,13 +15884,13 @@
         <v>0.9121087891210878</v>
       </c>
       <c r="L210" s="2" t="n">
-        <v>0.90625</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>0.8373294238673424</v>
+        <v>0.8257375864336783</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.0306969303069693</v>
+        <v>0.1456854314568543</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>88.45135245277227</v>
@@ -15911,7 +15911,7 @@
         <v>0.8921744779830265</v>
       </c>
       <c r="U210" s="2" t="n">
-        <v>0.0901909809019098</v>
+        <v>0.2394427223944272</v>
       </c>
     </row>
     <row r="211">
@@ -18734,10 +18734,10 @@
         <v>0.0104166666666666</v>
       </c>
       <c r="M249" s="2" t="n">
-        <v>0.0044530817139711</v>
+        <v>0.0038335074668716</v>
       </c>
       <c r="N249" s="2" t="n">
-        <v>0.1185881411858814</v>
+        <v>0.0948905109489051</v>
       </c>
       <c r="O249" s="2" t="n">
         <v>0.4688895925181455</v>
@@ -18758,7 +18758,7 @@
         <v>0.3762855611497761</v>
       </c>
       <c r="U249" s="2" t="n">
-        <v>0.1185881411858814</v>
+        <v>0.0948905109489051</v>
       </c>
     </row>
     <row r="250">
@@ -19096,13 +19096,13 @@
         <v>0.0001999800019998</v>
       </c>
       <c r="L254" s="2" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.03125</v>
       </c>
       <c r="M254" s="2" t="n">
-        <v>0.0285959635813768</v>
+        <v>0.0127726882694726</v>
       </c>
       <c r="N254" s="2" t="n">
-        <v>9.999000099990002e-05</v>
+        <v>0.0583941605839416</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>3.025006519895298</v>
@@ -19123,7 +19123,7 @@
         <v>9.142210703982063e-08</v>
       </c>
       <c r="U254" s="2" t="n">
-        <v>9.999000099990002e-05</v>
+        <v>0.0583941605839416</v>
       </c>
     </row>
     <row r="255">
@@ -19169,13 +19169,13 @@
         <v>0.017998200179982</v>
       </c>
       <c r="L255" s="2" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.2395833333333333</v>
       </c>
       <c r="M255" s="2" t="n">
-        <v>0.6653060927382026</v>
+        <v>0.2388176779670879</v>
       </c>
       <c r="N255" s="2" t="n">
-        <v>0.0040995900409959</v>
+        <v>0.4824517548245176</v>
       </c>
       <c r="O255" s="2" t="n">
         <v>69.91401723095377</v>
@@ -19196,7 +19196,7 @@
         <v>0.0205200976596203</v>
       </c>
       <c r="U255" s="2" t="n">
-        <v>0.008199180081991801</v>
+        <v>0.4824517548245176</v>
       </c>
     </row>
     <row r="256">
@@ -19242,13 +19242,13 @@
         <v>0.5835416458354165</v>
       </c>
       <c r="L256" s="2" t="n">
-        <v>0.28125</v>
+        <v>0.1041666666666666</v>
       </c>
       <c r="M256" s="2" t="n">
-        <v>0.2284987966083259</v>
+        <v>0.0787451239184199</v>
       </c>
       <c r="N256" s="2" t="n">
-        <v>0.1401859814018598</v>
+        <v>0.1687831216878312</v>
       </c>
       <c r="O256" s="2" t="n">
         <v>23.96902584921068</v>
@@ -19269,7 +19269,7 @@
         <v>0.2874609936819645</v>
       </c>
       <c r="U256" s="2" t="n">
-        <v>0.1401859814018598</v>
+        <v>0.3375662433756624</v>
       </c>
     </row>
   </sheetData>
@@ -19284,7 +19284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -19292,9 +19292,10 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19325,15 +19326,20 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>obs_both</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>obs_fraction</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>null_mean_fraction</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>p_relative</t>
         </is>
@@ -19362,12 +19368,15 @@
         <v>123</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>0.2764227642276423</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.1433526743128474</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>0.0001999800019998</v>
       </c>
     </row>
@@ -19394,13 +19403,16 @@
         <v>86</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.3953488372093023</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.2548579333054849</v>
+        <v>0.3837209302325581</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.0116988301169883</v>
+        <v>0.2171676126113322</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.0015998400159984</v>
       </c>
     </row>
     <row r="4">
@@ -19426,12 +19438,15 @@
         <v>123</v>
       </c>
       <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>0.024390243902439</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.009626788973925601</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>0.0854914508549145</v>
       </c>
     </row>
@@ -19458,12 +19473,15 @@
         <v>123</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>0.024390243902439</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.0108257402658217</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>0.1140885911408859</v>
       </c>
     </row>
@@ -19490,12 +19508,15 @@
         <v>123</v>
       </c>
       <c r="F6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>0.1056910569105691</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.061345913718756</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>0.0298970102989701</v>
       </c>
     </row>
@@ -19522,12 +19543,15 @@
         <v>123</v>
       </c>
       <c r="F7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>0.032520325203252</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.0006264774170982</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -19554,12 +19578,15 @@
         <v>123</v>
       </c>
       <c r="F8" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>0.6504065040650406</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.4483039261849628</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="I8" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -19586,12 +19613,15 @@
         <v>123</v>
       </c>
       <c r="F9" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>0.6178861788617886</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.4568752695688253</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.0005999400059994</v>
       </c>
     </row>
@@ -19618,13 +19648,16 @@
         <v>80</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.425</v>
+        <v>26</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.322426464950119</v>
+        <v>0.325</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.1022897710228977</v>
+        <v>0.1922229209604553</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.0128987101289871</v>
       </c>
     </row>
     <row r="11">
@@ -19650,12 +19683,15 @@
         <v>129</v>
       </c>
       <c r="F11" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>0.3023255813953488</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.1540111136186374</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="I11" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -19682,13 +19718,16 @@
         <v>91</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.4285714285714285</v>
+        <v>38</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.266543152352369</v>
+        <v>0.4175824175824176</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.0033996600339966</v>
+        <v>0.2296762896095168</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.0001999800019998</v>
       </c>
     </row>
     <row r="13">
@@ -19714,12 +19753,15 @@
         <v>129</v>
       </c>
       <c r="F13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>0.0232558139534883</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>0.012227987705091</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="I13" s="2" t="n">
         <v>0.1710828917108289</v>
       </c>
     </row>
@@ -19746,12 +19788,15 @@
         <v>129</v>
       </c>
       <c r="F14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>0.0232558139534883</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.0117558194369797</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="I14" s="2" t="n">
         <v>0.1540845915408459</v>
       </c>
     </row>
@@ -19778,12 +19823,15 @@
         <v>129</v>
       </c>
       <c r="F15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>0.1007751937984496</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>0.07218623604065399</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>0.1166883311668833</v>
       </c>
     </row>
@@ -19810,12 +19858,15 @@
         <v>129</v>
       </c>
       <c r="F16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>0.0310077519379844</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>0.0005923445810812</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="I16" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -19842,12 +19893,15 @@
         <v>129</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>0.6511627906976745</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>0.4587464387679191</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="I17" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -19874,12 +19928,15 @@
         <v>129</v>
       </c>
       <c r="F18" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G18" s="2" t="n">
         <v>0.6201550387596899</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>0.4749215736301728</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="I18" s="2" t="n">
         <v>0.0004999500049995</v>
       </c>
     </row>
@@ -19906,13 +19963,16 @@
         <v>84</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.4642857142857143</v>
+        <v>30</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.3381645265065893</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.0581941805819418</v>
+        <v>0.205254517019663</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0.004999500049995</v>
       </c>
     </row>
     <row r="20">
@@ -19938,12 +19998,15 @@
         <v>109</v>
       </c>
       <c r="F20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>0.2201834862385321</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>0.1315742055186048</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="I20" s="2" t="n">
         <v>0.0071992800719928</v>
       </c>
     </row>
@@ -19970,13 +20033,16 @@
         <v>72</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>23</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.243567145534435</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.07979202079792019</v>
+        <v>0.2004596473481762</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0.0171982801719828</v>
       </c>
     </row>
     <row r="22">
@@ -20002,12 +20068,15 @@
         <v>109</v>
       </c>
       <c r="F22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>0.018348623853211</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>0.009542453889522899</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>0.2232776722327767</v>
       </c>
     </row>
@@ -20034,12 +20103,15 @@
         <v>109</v>
       </c>
       <c r="F23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>0.0275229357798165</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>0.0115245328250493</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="I23" s="2" t="n">
         <v>0.0987901209879012</v>
       </c>
     </row>
@@ -20066,12 +20138,15 @@
         <v>109</v>
       </c>
       <c r="F24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="n">
         <v>0.073394495412844</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>0.0512603004709398</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>0.1530846915308469</v>
       </c>
     </row>
@@ -20098,12 +20173,15 @@
         <v>109</v>
       </c>
       <c r="F25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>0.036697247706422</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>0.0005026434118615</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="I25" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -20130,12 +20208,15 @@
         <v>109</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>0.5779816513761468</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>0.4314479951120569</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="I26" s="2" t="n">
         <v>0.0022997700229977</v>
       </c>
     </row>
@@ -20162,12 +20243,15 @@
         <v>109</v>
       </c>
       <c r="F27" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>0.5871559633027523</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>0.436995143574226</v>
       </c>
-      <c r="H27" s="2" t="n">
+      <c r="I27" s="2" t="n">
         <v>0.0008999100089991</v>
       </c>
     </row>
@@ -20194,13 +20278,16 @@
         <v>63</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.3809523809523809</v>
+        <v>17</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.3082634144400477</v>
+        <v>0.2698412698412698</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.188981101889811</v>
+        <v>0.1653702447117061</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0.0387961203879612</v>
       </c>
     </row>
     <row r="29">
@@ -20226,12 +20313,15 @@
         <v>121</v>
       </c>
       <c r="F29" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>0.2809917355371901</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.1421450842121935</v>
       </c>
-      <c r="H29" s="2" t="n">
+      <c r="I29" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -20258,13 +20348,16 @@
         <v>84</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.4047619047619047</v>
+        <v>33</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.2537413574373161</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.0070992900709929</v>
+        <v>0.214664883886876</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0.0006999300069993</v>
       </c>
     </row>
     <row r="31">
@@ -20290,12 +20383,15 @@
         <v>121</v>
       </c>
       <c r="F31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>0.024793388429752</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.0100717421131219</v>
       </c>
-      <c r="H31" s="2" t="n">
+      <c r="I31" s="2" t="n">
         <v>0.0952904709529047</v>
       </c>
     </row>
@@ -20322,12 +20418,15 @@
         <v>121</v>
       </c>
       <c r="F32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>0.024793388429752</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>0.0112391094807948</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="I32" s="2" t="n">
         <v>0.1218878112188781</v>
       </c>
     </row>
@@ -20354,12 +20453,15 @@
         <v>121</v>
       </c>
       <c r="F33" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G33" s="2" t="n">
         <v>0.1074380165289256</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>0.0636643563936522</v>
       </c>
-      <c r="H33" s="2" t="n">
+      <c r="I33" s="2" t="n">
         <v>0.0340965903409659</v>
       </c>
     </row>
@@ -20386,12 +20488,15 @@
         <v>121</v>
       </c>
       <c r="F34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" s="2" t="n">
         <v>0.0330578512396694</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>0.0006683079856507999</v>
       </c>
-      <c r="H34" s="2" t="n">
+      <c r="I34" s="2" t="n">
         <v>9.999000099990002e-05</v>
       </c>
     </row>
@@ -20418,12 +20523,15 @@
         <v>121</v>
       </c>
       <c r="F35" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G35" s="2" t="n">
         <v>0.6446280991735537</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>0.4452442239390236</v>
       </c>
-      <c r="H35" s="2" t="n">
+      <c r="I35" s="2" t="n">
         <v>0.0001999800019998</v>
       </c>
     </row>
@@ -20450,12 +20558,15 @@
         <v>121</v>
       </c>
       <c r="F36" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="G36" s="2" t="n">
         <v>0.6115702479338843</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.4591129064561725</v>
       </c>
-      <c r="H36" s="2" t="n">
+      <c r="I36" s="2" t="n">
         <v>0.0007999200079992</v>
       </c>
     </row>
@@ -20482,13 +20593,16 @@
         <v>78</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.4358974358974359</v>
+        <v>26</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.3220226738693063</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.07669233076692331</v>
+        <v>0.1872078505064105</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0.007999200079992001</v>
       </c>
     </row>
     <row r="38">
@@ -20514,12 +20628,15 @@
         <v>96</v>
       </c>
       <c r="F38" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G38" s="2" t="n">
         <v>0.2291666666666666</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>0.1162886414768563</v>
       </c>
-      <c r="H38" s="2" t="n">
+      <c r="I38" s="2" t="n">
         <v>0.0005999400059994</v>
       </c>
     </row>
@@ -20546,13 +20663,16 @@
         <v>62</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.3548387096774194</v>
+        <v>20</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.2326033893712875</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.0325967403259674</v>
+        <v>0.1809541405419664</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0.0058994100589941</v>
       </c>
     </row>
     <row r="40">
@@ -20578,12 +20698,15 @@
         <v>96</v>
       </c>
       <c r="F40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="n">
         <v>0.0104166666666666</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>0.0096248069523623</v>
       </c>
-      <c r="H40" s="2" t="n">
+      <c r="I40" s="2" t="n">
         <v>0.3190680931906809</v>
       </c>
     </row>
@@ -20610,12 +20733,15 @@
         <v>96</v>
       </c>
       <c r="F41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2" t="n">
         <v>0.0208333333333333</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>0.0111595214041916</v>
       </c>
-      <c r="H41" s="2" t="n">
+      <c r="I41" s="2" t="n">
         <v>0.1407859214078592</v>
       </c>
     </row>
@@ -20642,12 +20768,15 @@
         <v>96</v>
       </c>
       <c r="F42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" s="2" t="n">
         <v>0.0520833333333333</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>0.0329128510359453</v>
       </c>
-      <c r="H42" s="2" t="n">
+      <c r="I42" s="2" t="n">
         <v>0.140985901409859</v>
       </c>
     </row>
@@ -20674,12 +20803,15 @@
         <v>96</v>
       </c>
       <c r="F43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>0.0208333333333333</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>0.0009065570678966</v>
       </c>
-      <c r="H43" s="2" t="n">
+      <c r="I43" s="2" t="n">
         <v>0.0008999100089991</v>
       </c>
     </row>
@@ -20706,12 +20838,15 @@
         <v>96</v>
       </c>
       <c r="F44" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="G44" s="2" t="n">
         <v>0.53125</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>0.4133941587922883</v>
       </c>
-      <c r="H44" s="2" t="n">
+      <c r="I44" s="2" t="n">
         <v>0.008699130086991301</v>
       </c>
     </row>
@@ -20738,12 +20873,15 @@
         <v>96</v>
       </c>
       <c r="F45" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G45" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>0.3886211562607791</v>
       </c>
-      <c r="H45" s="2" t="n">
+      <c r="I45" s="2" t="n">
         <v>0.0014998500149985</v>
       </c>
     </row>
@@ -20770,17 +20908,20 @@
         <v>51</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.4313725490196078</v>
+        <v>16</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.2842780232997527</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.0465953404659534</v>
+        <v>0.1479957361521863</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0.0028997100289971</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H46"/>
+  <autoFilter ref="A1:I46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
